--- a/Document/Planning Centre JSON API Structure.xlsx
+++ b/Document/Planning Centre JSON API Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\GitHub\PlanningCenterScheduleUploader\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5080CA83-6FE7-4CA5-8A18-D5EAD93925A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FC5407-68F7-4830-BC5D-C641F55EA455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E09C4AAC-6BEB-4F82-B513-EA8E0E4C39CF}"/>
+    <workbookView xWindow="28680" yWindow="4455" windowWidth="20730" windowHeight="11160" xr2:uid="{E09C4AAC-6BEB-4F82-B513-EA8E0E4C39CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Centre JSON API Struct" sheetId="1" r:id="rId1"/>
@@ -102,331 +102,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="6" name="Group 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D24D3D29-F8FA-1BAD-2926-C3B391466EBE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="247650" y="555812"/>
-          <a:ext cx="2782420" cy="333375"/>
-          <a:chOff x="5067300" y="3095625"/>
-          <a:chExt cx="2800349" cy="333375"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="Rectangle: Rounded Corners 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35D993B9-BE3A-DFD7-3B32-11CC916A22F3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5067300" y="3095625"/>
-            <a:ext cx="2800349" cy="333375"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent3">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr lang="en-ZA" sz="1100"/>
-              <a:t>Key</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="5" name="Rectangle: Single Corner Snipped 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{415F0EF4-D7A9-5310-E3C8-D690D33D4BC9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6362700" y="3124200"/>
-            <a:ext cx="1466850" cy="276225"/>
-          </a:xfrm>
-          <a:prstGeom prst="snip1Rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent5">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr lang="en-ZA" sz="1100"/>
-              <a:t>Value</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="11" name="Group 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86E33CE6-34AF-AE60-4257-66970C6B23EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="238125" y="1022537"/>
-          <a:ext cx="2782420" cy="333375"/>
-          <a:chOff x="1924050" y="3571875"/>
-          <a:chExt cx="2800349" cy="333375"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="Rectangle: Rounded Corners 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D997E919-41B5-512B-25FF-0E6368974B61}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1924050" y="3571875"/>
-            <a:ext cx="2800349" cy="333375"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent3">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr lang="en-ZA" sz="1100"/>
-              <a:t>Key</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="Rectangle: Diagonal Corners Rounded 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70E81B2-E399-545C-91B5-BD5D5F68735F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3171825" y="3609975"/>
-            <a:ext cx="1504950" cy="257175"/>
-          </a:xfrm>
-          <a:prstGeom prst="round2DiagRect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent6">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent6"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent6"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr lang="en-ZA" sz="1100"/>
-              <a:t>Entity</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Rectangle: Diagonal Corners Snipped 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B91BD9F-25CD-4FC0-A1C3-1452CDE727F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1476376" y="1485900"/>
-          <a:ext cx="1495424" cy="276225"/>
-        </a:xfrm>
-        <a:prstGeom prst="snip2DiagRect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-ZA" sz="1100"/>
-            <a:t>Entities</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
